--- a/497-préparation-publication-release-204/ig/StructureDefinition-tddui-task-transport.xlsx
+++ b/497-préparation-publication-release-204/ig/StructureDefinition-tddui-task-transport.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.4.0-ballot</t>
+    <t>2.4.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T08:24:42+00:00</t>
+    <t>2026-07-22T08:41:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/497-préparation-publication-release-204/ig/StructureDefinition-tddui-task-transport.xlsx
+++ b/497-préparation-publication-release-204/ig/StructureDefinition-tddui-task-transport.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T08:41:38+00:00</t>
+    <t>2026-07-22T12:30:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
